--- a/Pruebas calificadas/COLEGIO PARQUES DE BOGOTÁ- DIAGNOSTICA- 902__CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO PARQUES DE BOGOTÁ- DIAGNOSTICA- 902__CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15212,7 +15212,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16220,7 +16220,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16726,7 +16726,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17232,7 +17232,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO PARQUES DE BOGOTÁ- DIAGNOSTICA- 902__CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO PARQUES DE BOGOTÁ- DIAGNOSTICA- 902__CALIFICADO.xlsx
@@ -938,9 +938,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -1191,9 +1191,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1444,9 +1444,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1946,9 +1946,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -2199,9 +2199,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -2448,9 +2448,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -2701,9 +2701,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -2954,9 +2954,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB10" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -3207,9 +3207,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB11" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -3713,9 +3713,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -3966,9 +3966,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB14" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -4219,9 +4219,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB15" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -4472,9 +4472,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB16" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -4978,9 +4978,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB18" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -5231,9 +5231,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB19" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -5484,9 +5484,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB20" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -5990,9 +5990,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB22" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -6243,9 +6243,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB23" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -6492,9 +6492,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB24" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -6998,9 +6998,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB26" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -7251,9 +7251,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB27" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -7757,9 +7757,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB29" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -8010,9 +8010,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB30" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -8512,9 +8512,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB32" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -9018,9 +9018,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB34" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO PARQUES DE BOGOTÁ- DIAGNOSTICA- 902__CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO PARQUES DE BOGOTÁ- DIAGNOSTICA- 902__CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1815,11 +1799,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -1827,7 +1807,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2068,11 +2048,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -2080,7 +2056,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2321,11 +2297,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -2333,7 +2305,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2570,11 +2542,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -2582,7 +2550,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2823,11 +2791,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -2835,7 +2799,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3076,11 +3040,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -3088,7 +3048,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3329,11 +3289,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -3341,7 +3297,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3582,11 +3538,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -3594,7 +3546,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3835,11 +3787,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -3847,7 +3795,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4088,11 +4036,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -4100,7 +4044,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4341,11 +4285,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -4353,7 +4293,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4594,11 +4534,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -4606,7 +4542,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4847,11 +4783,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -4859,7 +4791,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5100,11 +5032,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -5112,7 +5040,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5353,11 +5281,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -5365,7 +5289,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5606,11 +5530,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -5618,7 +5538,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5859,11 +5779,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -5871,7 +5787,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6112,11 +6028,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -6124,7 +6036,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6361,11 +6273,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -6373,7 +6281,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6614,11 +6522,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -6626,7 +6530,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6867,11 +6771,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -6879,7 +6779,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7120,11 +7020,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -7132,7 +7028,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7373,11 +7269,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -7385,7 +7277,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7626,11 +7518,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -7638,7 +7526,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7879,11 +7767,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -7891,7 +7775,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8132,11 +8016,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -8144,7 +8024,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8381,11 +8261,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -8393,7 +8269,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8634,11 +8510,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -8646,7 +8518,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8887,11 +8759,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -8899,7 +8767,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9140,11 +9008,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -9152,7 +9016,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9393,11 +9257,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -9405,7 +9265,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9646,11 +9506,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -9658,7 +9514,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9899,11 +9755,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -9911,7 +9763,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10152,11 +10004,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -10164,7 +10012,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10405,11 +10253,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -10417,7 +10261,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10658,11 +10502,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -10670,7 +10510,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10911,11 +10751,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -10923,7 +10759,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11164,11 +11000,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -11176,7 +11008,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11417,11 +11249,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -11429,7 +11257,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11670,11 +11498,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -11682,7 +11506,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11919,11 +11743,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -11931,7 +11751,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12168,11 +11988,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -12180,7 +11996,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12421,11 +12237,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -12433,7 +12245,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12670,11 +12482,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -12682,7 +12490,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12923,11 +12731,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -12935,7 +12739,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13176,11 +12980,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -13188,7 +12988,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13429,11 +13229,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -13441,7 +13237,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13682,11 +13478,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -13694,7 +13486,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13935,11 +13727,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -13947,7 +13735,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14188,11 +13976,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -14200,7 +13984,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14441,11 +14225,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -14453,7 +14233,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14694,11 +14474,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -14706,7 +14482,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14947,11 +14723,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -14959,7 +14731,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15200,11 +14972,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -15212,7 +14980,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15449,11 +15217,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -15461,7 +15225,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15702,11 +15466,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -15714,7 +15474,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15955,11 +15715,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -15967,7 +15723,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16208,11 +15964,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -16220,7 +15972,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16461,11 +16213,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -16473,7 +16221,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16714,11 +16462,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -16726,7 +16470,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16967,11 +16711,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -16979,7 +16719,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17220,11 +16960,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001800678</t>
@@ -17232,7 +16968,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO PARQUES DE BOGOTA (IED)</t>
+          <t>COLEGIO PARQUES DE BOGOTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
